--- a/artfynd/A 21662-2025 artfynd.xlsx
+++ b/artfynd/A 21662-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137253476</v>
       </c>
       <c r="B2" t="n">
-        <v>83483</v>
+        <v>83486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,7 +790,7 @@
         <v>137253496</v>
       </c>
       <c r="B3" t="n">
-        <v>83483</v>
+        <v>83486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1111,7 +1111,7 @@
         <v>137253488</v>
       </c>
       <c r="B6" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
         <v>137253491</v>
       </c>
       <c r="B7" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1325,7 +1325,7 @@
         <v>137253482</v>
       </c>
       <c r="B8" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2594,7 +2594,7 @@
         <v>137253470</v>
       </c>
       <c r="B20" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2701,7 +2701,7 @@
         <v>137253478</v>
       </c>
       <c r="B21" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Alexander Singer, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 21662-2025 artfynd.xlsx
+++ b/artfynd/A 21662-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137253476</v>
       </c>
       <c r="B2" t="n">
-        <v>83486</v>
+        <v>83496</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,7 +790,7 @@
         <v>137253496</v>
       </c>
       <c r="B3" t="n">
-        <v>83486</v>
+        <v>83496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -897,7 +897,7 @@
         <v>137253490</v>
       </c>
       <c r="B4" t="n">
-        <v>78519</v>
+        <v>78529</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1004,7 +1004,7 @@
         <v>137253469</v>
       </c>
       <c r="B5" t="n">
-        <v>79582</v>
+        <v>79592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1111,7 +1111,7 @@
         <v>137253488</v>
       </c>
       <c r="B6" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
         <v>137253491</v>
       </c>
       <c r="B7" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1325,7 +1325,7 @@
         <v>137253482</v>
       </c>
       <c r="B8" t="n">
-        <v>83499</v>
+        <v>83509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
         <v>137253474</v>
       </c>
       <c r="B9" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
         <v>137253485</v>
       </c>
       <c r="B10" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1636,7 +1636,7 @@
         <v>137253489</v>
       </c>
       <c r="B11" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1743,7 +1743,7 @@
         <v>137253495</v>
       </c>
       <c r="B12" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1850,7 +1850,7 @@
         <v>137253500</v>
       </c>
       <c r="B13" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1957,7 +1957,7 @@
         <v>137253471</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2064,7 +2064,7 @@
         <v>137253479</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2166,7 +2166,7 @@
         <v>137253480</v>
       </c>
       <c r="B16" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2273,7 +2273,7 @@
         <v>137253484</v>
       </c>
       <c r="B17" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2380,7 +2380,7 @@
         <v>137253487</v>
       </c>
       <c r="B18" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2487,7 +2487,7 @@
         <v>137253493</v>
       </c>
       <c r="B19" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2594,7 +2594,7 @@
         <v>137253470</v>
       </c>
       <c r="B20" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2701,7 +2701,7 @@
         <v>137253478</v>
       </c>
       <c r="B21" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2808,7 +2808,7 @@
         <v>137253472</v>
       </c>
       <c r="B22" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2910,7 +2910,7 @@
         <v>137253492</v>
       </c>
       <c r="B23" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3017,7 +3017,7 @@
         <v>137253499</v>
       </c>
       <c r="B24" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3124,7 +3124,7 @@
         <v>137253481</v>
       </c>
       <c r="B25" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3226,7 +3226,7 @@
         <v>137253498</v>
       </c>
       <c r="B26" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3252,6 +3252,10 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skogen mellan Brånaberg och Gurisviken, Ly lm</t>
@@ -3313,7 +3317,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3328,7 +3332,7 @@
         <v>137253483</v>
       </c>
       <c r="B27" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3354,6 +3358,10 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skogen mellan Brånaberg och Gurisviken, Ly lm</t>
@@ -3420,7 +3428,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3435,7 +3443,7 @@
         <v>137253497</v>
       </c>
       <c r="B28" t="n">
-        <v>78508</v>
+        <v>78518</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,7 +3535,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alexander Singer, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 21662-2025 artfynd.xlsx
+++ b/artfynd/A 21662-2025 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>137253488</v>
       </c>
       <c r="B6" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137253491</v>
       </c>
       <c r="B7" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 21662-2025 artfynd.xlsx
+++ b/artfynd/A 21662-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137253476</v>
       </c>
       <c r="B2" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137253496</v>
       </c>
       <c r="B3" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137253490</v>
       </c>
       <c r="B4" t="n">
-        <v>78529</v>
+        <v>78532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137253469</v>
       </c>
       <c r="B5" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137253488</v>
       </c>
       <c r="B6" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137253491</v>
       </c>
       <c r="B7" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137253482</v>
       </c>
       <c r="B8" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137253474</v>
       </c>
       <c r="B9" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>137253485</v>
       </c>
       <c r="B10" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137253489</v>
       </c>
       <c r="B11" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>137253495</v>
       </c>
       <c r="B12" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137253500</v>
       </c>
       <c r="B13" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>137253471</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>137253479</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>137253480</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137253484</v>
       </c>
       <c r="B17" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>137253487</v>
       </c>
       <c r="B18" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>137253493</v>
       </c>
       <c r="B19" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>137253470</v>
       </c>
       <c r="B20" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137253478</v>
       </c>
       <c r="B21" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>137253472</v>
       </c>
       <c r="B22" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>137253492</v>
       </c>
       <c r="B23" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>137253499</v>
       </c>
       <c r="B24" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>137253481</v>
       </c>
       <c r="B25" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>137253498</v>
       </c>
       <c r="B26" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>137253483</v>
       </c>
       <c r="B27" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>137253497</v>
       </c>
       <c r="B28" t="n">
-        <v>78518</v>
+        <v>78521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 21662-2025 artfynd.xlsx
+++ b/artfynd/A 21662-2025 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>137253488</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137253491</v>
       </c>
       <c r="B7" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 21662-2025 artfynd.xlsx
+++ b/artfynd/A 21662-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137253476</v>
       </c>
       <c r="B2" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137253496</v>
       </c>
       <c r="B3" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137253490</v>
       </c>
       <c r="B4" t="n">
-        <v>78532</v>
+        <v>78537</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137253469</v>
       </c>
       <c r="B5" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137253488</v>
       </c>
       <c r="B6" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137253491</v>
       </c>
       <c r="B7" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137253482</v>
       </c>
       <c r="B8" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137253474</v>
       </c>
       <c r="B9" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>137253485</v>
       </c>
       <c r="B10" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137253489</v>
       </c>
       <c r="B11" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>137253495</v>
       </c>
       <c r="B12" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137253500</v>
       </c>
       <c r="B13" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>137253471</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>137253479</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>137253480</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137253484</v>
       </c>
       <c r="B17" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>137253487</v>
       </c>
       <c r="B18" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>137253493</v>
       </c>
       <c r="B19" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>137253470</v>
       </c>
       <c r="B20" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137253478</v>
       </c>
       <c r="B21" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>137253472</v>
       </c>
       <c r="B22" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>137253492</v>
       </c>
       <c r="B23" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>137253499</v>
       </c>
       <c r="B24" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>137253481</v>
       </c>
       <c r="B25" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>137253498</v>
       </c>
       <c r="B26" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>137253483</v>
       </c>
       <c r="B27" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>137253497</v>
       </c>
       <c r="B28" t="n">
-        <v>78521</v>
+        <v>78526</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 21662-2025 artfynd.xlsx
+++ b/artfynd/A 21662-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137253476</v>
       </c>
       <c r="B2" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137253496</v>
       </c>
       <c r="B3" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137253490</v>
       </c>
       <c r="B4" t="n">
-        <v>78537</v>
+        <v>78548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137253469</v>
       </c>
       <c r="B5" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137253488</v>
       </c>
       <c r="B6" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137253491</v>
       </c>
       <c r="B7" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137253482</v>
       </c>
       <c r="B8" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137253474</v>
       </c>
       <c r="B9" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>137253485</v>
       </c>
       <c r="B10" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137253489</v>
       </c>
       <c r="B11" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>137253495</v>
       </c>
       <c r="B12" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137253500</v>
       </c>
       <c r="B13" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>137253471</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>137253479</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>137253480</v>
       </c>
       <c r="B16" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137253484</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>137253487</v>
       </c>
       <c r="B18" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>137253493</v>
       </c>
       <c r="B19" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>137253470</v>
       </c>
       <c r="B20" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137253478</v>
       </c>
       <c r="B21" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>137253472</v>
       </c>
       <c r="B22" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>137253492</v>
       </c>
       <c r="B23" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>137253499</v>
       </c>
       <c r="B24" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>137253481</v>
       </c>
       <c r="B25" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>137253497</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>78537</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 21662-2025 artfynd.xlsx
+++ b/artfynd/A 21662-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137253476</v>
       </c>
       <c r="B2" t="n">
-        <v>83515</v>
+        <v>83516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137253496</v>
       </c>
       <c r="B3" t="n">
-        <v>83515</v>
+        <v>83516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137253490</v>
       </c>
       <c r="B4" t="n">
-        <v>78548</v>
+        <v>78549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137253469</v>
       </c>
       <c r="B5" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137253488</v>
       </c>
       <c r="B6" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137253491</v>
       </c>
       <c r="B7" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137253482</v>
       </c>
       <c r="B8" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137253474</v>
       </c>
       <c r="B9" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>137253485</v>
       </c>
       <c r="B10" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137253489</v>
       </c>
       <c r="B11" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>137253495</v>
       </c>
       <c r="B12" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137253500</v>
       </c>
       <c r="B13" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>137253471</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>137253479</v>
       </c>
       <c r="B15" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>137253480</v>
       </c>
       <c r="B16" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137253484</v>
       </c>
       <c r="B17" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>137253487</v>
       </c>
       <c r="B18" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>137253493</v>
       </c>
       <c r="B19" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>137253470</v>
       </c>
       <c r="B20" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137253478</v>
       </c>
       <c r="B21" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>137253472</v>
       </c>
       <c r="B22" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>137253492</v>
       </c>
       <c r="B23" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>137253499</v>
       </c>
       <c r="B24" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>137253481</v>
       </c>
       <c r="B25" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>137253497</v>
       </c>
       <c r="B28" t="n">
-        <v>78537</v>
+        <v>78538</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 21662-2025 artfynd.xlsx
+++ b/artfynd/A 21662-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137253476</v>
       </c>
       <c r="B2" t="n">
-        <v>83516</v>
+        <v>83518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137253496</v>
       </c>
       <c r="B3" t="n">
-        <v>83516</v>
+        <v>83518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137253490</v>
       </c>
       <c r="B4" t="n">
-        <v>78549</v>
+        <v>78551</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137253469</v>
       </c>
       <c r="B5" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137253488</v>
       </c>
       <c r="B6" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137253491</v>
       </c>
       <c r="B7" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137253482</v>
       </c>
       <c r="B8" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137253474</v>
       </c>
       <c r="B9" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>137253485</v>
       </c>
       <c r="B10" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137253489</v>
       </c>
       <c r="B11" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>137253495</v>
       </c>
       <c r="B12" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137253500</v>
       </c>
       <c r="B13" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>137253471</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>137253479</v>
       </c>
       <c r="B15" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>137253480</v>
       </c>
       <c r="B16" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137253484</v>
       </c>
       <c r="B17" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>137253487</v>
       </c>
       <c r="B18" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>137253493</v>
       </c>
       <c r="B19" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>137253470</v>
       </c>
       <c r="B20" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137253478</v>
       </c>
       <c r="B21" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>137253472</v>
       </c>
       <c r="B22" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>137253492</v>
       </c>
       <c r="B23" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>137253499</v>
       </c>
       <c r="B24" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>137253481</v>
       </c>
       <c r="B25" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>137253497</v>
       </c>
       <c r="B28" t="n">
-        <v>78538</v>
+        <v>78540</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 21662-2025 artfynd.xlsx
+++ b/artfynd/A 21662-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137253476</v>
       </c>
       <c r="B2" t="n">
-        <v>83518</v>
+        <v>83522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137253496</v>
       </c>
       <c r="B3" t="n">
-        <v>83518</v>
+        <v>83522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137253490</v>
       </c>
       <c r="B4" t="n">
-        <v>78551</v>
+        <v>78555</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137253469</v>
       </c>
       <c r="B5" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137253488</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137253491</v>
       </c>
       <c r="B7" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137253482</v>
       </c>
       <c r="B8" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137253474</v>
       </c>
       <c r="B9" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>137253485</v>
       </c>
       <c r="B10" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137253489</v>
       </c>
       <c r="B11" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>137253495</v>
       </c>
       <c r="B12" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137253500</v>
       </c>
       <c r="B13" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>137253471</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>137253479</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>137253480</v>
       </c>
       <c r="B16" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137253484</v>
       </c>
       <c r="B17" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>137253487</v>
       </c>
       <c r="B18" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>137253493</v>
       </c>
       <c r="B19" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>137253470</v>
       </c>
       <c r="B20" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137253478</v>
       </c>
       <c r="B21" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>137253472</v>
       </c>
       <c r="B22" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>137253492</v>
       </c>
       <c r="B23" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>137253499</v>
       </c>
       <c r="B24" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>137253481</v>
       </c>
       <c r="B25" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>137253498</v>
       </c>
       <c r="B26" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>137253483</v>
       </c>
       <c r="B27" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>137253497</v>
       </c>
       <c r="B28" t="n">
-        <v>78540</v>
+        <v>78544</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
